--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260727.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260727.xlsx
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>124,500</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>124,500</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>750,000</t>
+          <t>1,800,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,800,000</t>
+          <t>750,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>760,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>760,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
